--- a/result.xlsx
+++ b/result.xlsx
@@ -413,23 +413,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>05-3841</t>
+          <t>05-1</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>26.09.2026</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>ЗАО БеСТ</t>
+          <t>ООО «Белорусские облачные технологии»</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -444,49 +444,12 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Область</t>
+          <t>Город</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>1921, Минская обл., Мядельский р-н., н.п. Свирь, ул. Советская, 29</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>05-3842</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>23.09.2026</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ООО Белорусский облачные технологии</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>ЭМИ РЧ</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Город</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>700034, Минская обл., Минский р-н., н.п. Минск, ул. Шаранговича, 39</t>
+          <t>702225, Минская обл., Минский р-н., н.п. Минск, ул. Притыцкого, 148 (ул. Кунцевщина, 2а)</t>
         </is>
       </c>
     </row>
